--- a/Entry_and_Exist_report/output/Entry_and_Exit_of_Bus.xlsx
+++ b/Entry_and_Exist_report/output/Entry_and_Exit_of_Bus.xlsx
@@ -8,7 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TSegregated Report2025-08-24" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TSegregated Report2025-08-21" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TSegregated Report2025-08-26" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TSegregated Report2025-08-25" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TSegregated Report2025-08-24" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="TSegregated Report2025-08-23" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -267,6 +271,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -313,10 +321,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -682,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -718,18 +722,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>S.
 NO</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>NMC
 COUNT
@@ -738,119 +742,119 @@
 REPORT</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>DELIVERY STATUS BETWEEN
 5 AM TO 10 AM</t>
         </is>
       </c>
-      <c r="E1" s="10" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>REPORTED DEFECTS AND RELEASED STATUS TILL 10 AM</t>
         </is>
       </c>
-      <c r="H1" s="10" t="n"/>
-      <c r="I1" s="10" t="n"/>
-      <c r="J1" s="10" t="n"/>
-      <c r="K1" s="10" t="n"/>
-      <c r="L1" s="10" t="n"/>
-      <c r="M1" s="10" t="n"/>
-      <c r="N1" s="10" t="n"/>
-      <c r="O1" s="10" t="n"/>
-      <c r="P1" s="10" t="n"/>
-      <c r="Q1" s="10" t="n"/>
-      <c r="R1" s="10" t="n"/>
-      <c r="S1" s="10" t="n"/>
-      <c r="T1" s="10" t="n"/>
-      <c r="U1" s="10" t="n"/>
-      <c r="V1" s="10" t="n"/>
-      <c r="W1" s="10" t="n"/>
-      <c r="X1" s="11" t="n"/>
-      <c r="Z1" s="9" t="inlineStr">
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="14" t="n"/>
+      <c r="L1" s="14" t="n"/>
+      <c r="M1" s="14" t="n"/>
+      <c r="N1" s="14" t="n"/>
+      <c r="O1" s="14" t="n"/>
+      <c r="P1" s="14" t="n"/>
+      <c r="Q1" s="14" t="n"/>
+      <c r="R1" s="14" t="n"/>
+      <c r="S1" s="14" t="n"/>
+      <c r="T1" s="14" t="n"/>
+      <c r="U1" s="14" t="n"/>
+      <c r="V1" s="14" t="n"/>
+      <c r="W1" s="14" t="n"/>
+      <c r="X1" s="15" t="n"/>
+      <c r="Z1" s="13" t="inlineStr">
         <is>
           <t>VARIANCE BETWEEN
 PROJECT REPORT AND WORKSHOP REPORT</t>
         </is>
       </c>
-      <c r="AA1" s="10" t="n"/>
-      <c r="AB1" s="10" t="n"/>
-      <c r="AC1" s="11" t="n"/>
-      <c r="AD1" s="12" t="n"/>
+      <c r="AA1" s="14" t="n"/>
+      <c r="AB1" s="14" t="n"/>
+      <c r="AC1" s="15" t="n"/>
+      <c r="AD1" s="16" t="n"/>
     </row>
     <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="13" t="n"/>
-      <c r="B2" s="13" t="n"/>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="A2" s="17" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>REPORTED
 TO
 W/SHOP</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>RELEASED</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="18" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="H2" s="15" t="n"/>
-      <c r="I2" s="16" t="n"/>
-      <c r="J2" s="14" t="inlineStr">
+      <c r="H2" s="19" t="n"/>
+      <c r="I2" s="20" t="n"/>
+      <c r="J2" s="18" t="inlineStr">
         <is>
           <t>TYRE</t>
         </is>
       </c>
-      <c r="K2" s="15" t="n"/>
-      <c r="L2" s="16" t="n"/>
-      <c r="M2" s="14" t="inlineStr">
+      <c r="K2" s="19" t="n"/>
+      <c r="L2" s="20" t="n"/>
+      <c r="M2" s="18" t="inlineStr">
         <is>
           <t>MECH</t>
         </is>
       </c>
-      <c r="N2" s="15" t="n"/>
-      <c r="O2" s="16" t="n"/>
-      <c r="P2" s="14" t="inlineStr">
+      <c r="N2" s="19" t="n"/>
+      <c r="O2" s="20" t="n"/>
+      <c r="P2" s="18" t="inlineStr">
         <is>
           <t>BODY</t>
         </is>
       </c>
-      <c r="Q2" s="15" t="n"/>
-      <c r="R2" s="16" t="n"/>
-      <c r="S2" s="14" t="inlineStr">
+      <c r="Q2" s="19" t="n"/>
+      <c r="R2" s="20" t="n"/>
+      <c r="S2" s="18" t="inlineStr">
         <is>
           <t>A C &amp; ELE</t>
         </is>
       </c>
-      <c r="T2" s="15" t="n"/>
-      <c r="U2" s="16" t="n"/>
-      <c r="V2" s="14" t="inlineStr">
+      <c r="T2" s="19" t="n"/>
+      <c r="U2" s="20" t="n"/>
+      <c r="V2" s="18" t="inlineStr">
         <is>
           <t>W/S OR
 WINDOW
 GLASS</t>
         </is>
       </c>
-      <c r="W2" s="15" t="n"/>
-      <c r="X2" s="16" t="n"/>
-      <c r="Z2" s="17" t="inlineStr">
+      <c r="W2" s="19" t="n"/>
+      <c r="X2" s="20" t="n"/>
+      <c r="Z2" s="21" t="inlineStr">
         <is>
           <t>Total
 Differences</t>
         </is>
       </c>
-      <c r="AA2" s="17" t="inlineStr">
+      <c r="AA2" s="21" t="inlineStr">
         <is>
           <t>REPORTED
 AFTER 10 AM
@@ -858,19 +862,19 @@
 SAME DAY</t>
         </is>
       </c>
-      <c r="AB2" s="17" t="inlineStr">
+      <c r="AB2" s="21" t="inlineStr">
         <is>
           <t>RELEASED
 ON THE
 SAME DAY</t>
         </is>
       </c>
-      <c r="AC2" s="17" t="inlineStr">
+      <c r="AC2" s="21" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="AD2" s="17" t="inlineStr">
+      <c r="AD2" s="21" t="inlineStr">
         <is>
           <t>NOT
 REPORTED
@@ -880,366 +884,747 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="12" t="n"/>
-      <c r="B3" s="12" t="n"/>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="12" t="n"/>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="A3" s="16" t="n"/>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="J3" s="12" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="K3" s="12" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="M3" s="12" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="N3" s="12" t="inlineStr">
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="O3" s="12" t="inlineStr">
+      <c r="O3" s="16" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="P3" s="12" t="inlineStr">
+      <c r="P3" s="16" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="Q3" s="12" t="inlineStr">
+      <c r="Q3" s="16" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="R3" s="12" t="inlineStr">
+      <c r="R3" s="16" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="S3" s="12" t="inlineStr">
+      <c r="S3" s="16" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="T3" s="12" t="inlineStr">
+      <c r="T3" s="16" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="U3" s="12" t="inlineStr">
+      <c r="U3" s="16" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="V3" s="12" t="inlineStr">
+      <c r="V3" s="16" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="W3" s="12" t="inlineStr">
+      <c r="W3" s="16" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="X3" s="12" t="inlineStr">
+      <c r="X3" s="16" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Z3" s="18" t="n"/>
-      <c r="AA3" s="18" t="n"/>
-      <c r="AB3" s="18" t="n"/>
-      <c r="AC3" s="18" t="n"/>
-      <c r="AD3" s="18" t="n"/>
+      <c r="Z3" s="22" t="n"/>
+      <c r="AA3" s="22" t="n"/>
+      <c r="AB3" s="22" t="n"/>
+      <c r="AC3" s="22" t="n"/>
+      <c r="AD3" s="22" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="19" t="n">
+      <c r="A4" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="n">
+        <v>21</v>
+      </c>
+      <c r="D4" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="O4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Z4" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA4" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB4" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="D5" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" s="23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="N5" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="O5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Z5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="C4" s="19" t="n">
+      <c r="C6" s="23" t="n">
         <v>37</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D6" s="23" t="n">
         <v>34</v>
       </c>
-      <c r="E4" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="F4" s="19" t="n">
+      <c r="E6" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="N6" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="O6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="19" t="n">
+      <c r="Q6" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="19" t="n">
+      <c r="S6" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="V6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="W6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Z6" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="N7" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="O7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Z7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>21</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="K8" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="L4" s="19" t="n">
+      <c r="L8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="N4" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="O4" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="P4" s="19" t="n">
+      <c r="M8" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="N8" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="O8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Z8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="n">
+        <v>131</v>
+      </c>
+      <c r="D9" s="24" t="n">
+        <v>119</v>
+      </c>
+      <c r="E9" s="24" t="n">
+        <v>116</v>
+      </c>
+      <c r="F9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="24" t="n">
+        <v>85</v>
+      </c>
+      <c r="K9" s="24" t="n">
+        <v>84</v>
+      </c>
+      <c r="L9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="N9" s="24" t="n">
+        <v>34</v>
+      </c>
+      <c r="O9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q9" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="R9" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="U9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA9" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB9" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="Q4" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="U4" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Z4" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA4" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="19" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="n">
-        <v>37</v>
-      </c>
-      <c r="D5" s="20" t="n">
-        <v>34</v>
-      </c>
-      <c r="E5" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="F5" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="K5" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="L5" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="N5" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="O5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="U5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA5" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD5" s="20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1"/>
-    <row r="7" ht="50" customHeight="1">
-      <c r="B7" s="21" t="inlineStr">
+    </row>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="50" customHeight="1">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>NO: OF BUSES
 REPORTED WITHIN 5 HRS</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="23" t="n">
-        <v>34</v>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="27" t="n">
+        <v>119</v>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>NO: OF BUSES
 RELEASED</t>
         </is>
       </c>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="23" t="n">
-        <v>29</v>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="G11" s="26" t="n"/>
+      <c r="H11" s="27" t="n">
+        <v>116</v>
+      </c>
+      <c r="J11" s="25" t="inlineStr">
         <is>
           <t>OUTPUT
 EFFICIENCY</t>
         </is>
       </c>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="23" t="inlineStr">
-        <is>
-          <t>85.3%</t>
-        </is>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
+      <c r="K11" s="26" t="n"/>
+      <c r="L11" s="27" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="N11" s="25" t="inlineStr">
         <is>
           <t>NO: OF BUSES NOT
 REPORTED ON THE SAME DAY</t>
         </is>
       </c>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1"/>
-    <row r="9" ht="20" customHeight="1"/>
-    <row r="10" ht="20" customHeight="1"/>
+      <c r="O11" s="26" t="n"/>
+      <c r="P11" s="26" t="n"/>
+      <c r="Q11" s="27" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F11:G11"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="Z2:Z3"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="AB2:AB3"/>
     <mergeCell ref="AD2:AD3"/>
     <mergeCell ref="J2:L2"/>
+    <mergeCell ref="J11:K11"/>
     <mergeCell ref="G1:X1"/>
-    <mergeCell ref="J7:K7"/>
     <mergeCell ref="AA2:AA3"/>
     <mergeCell ref="AC2:AC3"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="V2:X2"/>
+    <mergeCell ref="N11:P11"/>
     <mergeCell ref="G2:I2"/>
-    <mergeCell ref="N7:P7"/>
     <mergeCell ref="Z1:AD1"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="S2:U2"/>
@@ -1250,6 +1635,4191 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="94" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Work Order Status Report</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+      <c r="K1" s="8" t="n"/>
+      <c r="L1" s="9" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Date of B/D</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Time of B/D</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Driver Emp No #</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Asset Number</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Bus No.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Type Of B/D</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Operation Action</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Re-Operations time</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>W/S Comments</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>workshop reported time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0.2458333333333333</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>2184268</v>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>PTS1409</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>92/9540</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Front   Right  Side  Socket  Ambrose  Road  Broken  Check &amp;   Replace </t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 06:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2144096</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>PTS1543</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>92/9512</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Murughab</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Air   Leaks  &amp;  Radiator  Need   To  washing  Cling  </t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2234048</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>PTS1265</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>92/6893</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Murughab</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Rear LHS balloon </t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.3152777777777778</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2244054</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>PTS1271</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>92/6910</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OVER HEAT AIR LEAK</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.3506944444444444</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234118 </t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>PTS1459</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>92/9497</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts  </t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Over   Heat   &amp;  Air  Leaks  &amp;  All  Lighting  Systems   Check &amp;  Repairs </t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.3472222222222222</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2184477</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>PTS1359</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>92/9010</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shariq  To  pts  </t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Air   Leaks  &amp;  Radiator  Need   To  washing  Cling  </t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 10:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 8:52</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234081 </t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>PTS1435</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>92/9487</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maliya </t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Rear LHS balloon </t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 13:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 9:00</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174225 </t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>PTS1338</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>92/6968</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OVER HEAT AIR LEAK</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 13:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.4131944444444444</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234120 </t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>PTS1324</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>92/6933</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Jleeb to pts </t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Over   Heat   &amp;  Air  Leaks  &amp;  All  Lighting  Systems   Check &amp;  Repairs </t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
+      <c r="M12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.2152777777777778</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174279 </t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>PTS1297</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>92/6906</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> A/C  Not  Working  &amp; Over  Heat </t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 06:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ELE, MECH</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.2152777777777778</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2244077</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>PTS1389</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>92/9518</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Starting  Defect  &amp;  Check &amp; Replace  Battery   New    &amp;  On  Running  Time  Engine   Off </t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 06:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>TYRE, MECH</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2194093</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>PTS1241</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>92/6918</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Steering   Wheel    Hard &amp;  Jam Tide Check   Oil  </t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 06:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234048 </t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>PTS1265</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>92/6893</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts  </t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Brake  Adjusting   &amp;   Right Side Front   Wheel   Sound   Coming  &amp; Socket  Ambrose  Check </t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.3368055555555556</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2194125 </t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>PTS1393</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>92/9421</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kahiatn To pts  </t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Front   Balloon  Air   Leaks  &amp; Steering  Wheel    wobbling   Too  Much </t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2244021 </t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>PTS1538</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>92/9447</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JleEB To Pts  </t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Brake  Adjusting   &amp;   Right Side Front   Wheel   Sound   Coming  &amp; Socket  Ambrose  Check </t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2144340 </t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>PTS1367</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>92/9018</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jleeb To Pts  </t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Front   Balloon  Air   Leaks  &amp; Steering  Wheel    wobbling   Too  Much </t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="7" t="n"/>
+      <c r="K22" s="7" t="n"/>
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>BODY</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0.2638888888888889</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>2189056</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>PTS1332</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>92/6885</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Murughab</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Front   Door   Switch   Defect  </t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 10:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0.3229166666666667</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174235 </t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>PTS1493</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>92/9452</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts </t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRONT DOOR DEFAECT  </t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 10:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.3194444444444444</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184020 </t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>PTS1557</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>92/9545</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jleeb  to pts  </t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mirror frame RHS DEFECT  </t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 10:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 9:04</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2189085 </t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>PTS1248</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>92/7013</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRONT DOOR DEFAECT  </t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21 13:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 9:36</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174231 </t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>PTS1249</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>92/6944</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MALIAY </t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mirror frame RHS DEFECT  </t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="7" t="n"/>
+      <c r="K28" s="7" t="n"/>
+      <c r="L28" s="7" t="n"/>
+      <c r="M28" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A3:A12"/>
+    <mergeCell ref="A23:A28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="68" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Work Order Status Report</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+      <c r="K1" s="8" t="n"/>
+      <c r="L1" s="9" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Date of B/D</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Time of B/D</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Driver Emp No #</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Asset Number</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Bus No.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Type Of B/D</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Operation Action</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Re-Operations time</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>W/S Comments</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>workshop reported time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ELE, MECH</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>2174206</v>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>PTS1287</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>92/7003</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>A/C Belt Broken</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 06:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
+      <c r="L4" s="7" t="n"/>
+      <c r="M4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>92/6953</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>PTS1321</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>92/6953</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Rear Right Side Both Tires Burst</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.2701388888888889</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2184557</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>PTS1260</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>92/6946</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HASAWI </t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air leak </t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2234004</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>PTS1421</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>92/9435</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliay  </t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poor brake ,  steering play ,  vibration </t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.2965277777777778</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2184157</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>PTS1263</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>92/6887</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Air  leak </t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.3173611111111111</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2184540</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>PTS1354</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>92/9005</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Mirqab</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air leak </t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.3305555555555555</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2184116</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>PTS1436</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>92/9469</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>mirqab</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gear slipping </t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.3402777777777778</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2224033 </t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>PTS1476</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>92/9532</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jleeb to pts </t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Brake  Adjusting &amp; Balloon  Defect Sound Coming </t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2064054 </t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>PTS1243</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>92/6912</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Riggae To pts </t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Over  Heat  &amp;    Water   Leaks &amp; Brake &amp;  Hand   Brake   Defect  </t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 10:00</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184337 </t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>PTS1206</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>92/6922</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Farwaniya   To pts </t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Brake   Defect </t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 11:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ELE, TYRE, MECH</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>92/6939</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>PTS1252</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>92/6939</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Oil pressure sensor defect</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>MECH, BODY</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0.2423611111111111</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>2134366</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>PTS1585</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>92/9411</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Air leak , cabin  door  defect</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 13:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0.3993055555555556</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2194129</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>MOE353</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>92/8951</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shuwaikh  to g1 </t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Front   Door   air  Leaks </t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>TYRE</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.2444444444444444</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>2244078</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>PTS1447</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>92/9557</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear Right side outer tire puncher </t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.3305555555555555</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>2174033</v>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>PTS1506</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>92/9578</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salmiya </t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear left side outer tire puncher </t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2104071 </t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>PTS1374</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>92/9025</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shaban To pts  </t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Left Side Rear   Inner  Tire   Puncher </t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0.3645833333333333</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2162333</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>PTS1490</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>92/9474</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts  </t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Right  Rear  Outer  Tire  Blast  </t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174258 </t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>PTS1358</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>92/9009</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salmiya  to pts  </t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Right  Side  Rear  Inner  Tire  Blast </t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.3993055555555556</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234087 </t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>PTS1244</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>92/6891</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts  </t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> All  Tire   Air  Check &amp;  Horan  Not  Working  </t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
+      <c r="J26" s="7" t="n"/>
+      <c r="K26" s="7" t="n"/>
+      <c r="L26" s="7" t="n"/>
+      <c r="M26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.2930555555555556</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>2174307</v>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>PTS1495</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>92/9419</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Poor  pick  up , A/c defect</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="7" t="n"/>
+      <c r="K28" s="7" t="n"/>
+      <c r="L28" s="7" t="n"/>
+      <c r="M28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>TYRE, BODY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0.2965277777777778</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>2244033</v>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>PTS1373</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>92/9024</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Front   door defect , Rear Right side tire need Replacement </t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-26 09:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="7" t="n"/>
+      <c r="K30" s="7" t="n"/>
+      <c r="L30" s="7" t="n"/>
+      <c r="M30" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A5:A14"/>
+    <mergeCell ref="A20:A26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="127" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Work Order Status Report</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+      <c r="K1" s="8" t="n"/>
+      <c r="L1" s="9" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Date of B/D</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Time of B/D</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Driver Emp No #</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Asset Number</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Bus No.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Type Of B/D</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Operation Action</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Re-Operations time</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>W/S Comments</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>workshop reported time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ELE, MECH</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0.2340277777777778</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>2064054</v>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>PTS1422</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>92/9574</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Reggai</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>A/c pulley    sound</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2244002 </t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>PTS1356</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>92/9007</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jleeb To pts  </t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> A/C  Blower Not  Working &amp;  Horan &amp;  Brake   Adjusting   </t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>MECH, BODY</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2053309</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>PTS1340</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>92/6874</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Farwaniya </t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Break Defect &amp; Front Door Air Leak </t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
+      <c r="M7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.2743055555555556</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2244069 </t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>PTS1237</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>92/6924</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kaithan </t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Over Heat &amp; A/C Cut Off </t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 09:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TYRE</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.2784722222222222</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2134479</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>PTS1361</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>92/9012</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear Right side inner tire puncher </t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 08:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.2861111111111111</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2234068</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>PTS1280</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>92/6890</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliya </t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear Right side  Outer   tire  puncher </t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 09:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0.2951388888888889</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2174529</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>MOE331</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>92/8929</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>PTS G1</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear Right side outer tire blast ,  poor pick up </t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174231 </t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>PTS1249</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>92/6944</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts </t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Horan &amp;  Right   Side Rear  Inner  Tire  Puncher </t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234095 </t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>PTS1262</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>92/6983</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Murgab to pts  </t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Right  Side  Rear  Inner  Tire   Puncher </t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>ELE, BODY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2234100</v>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>PTS1416</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>92/9501</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliya </t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuse box door lock defect  </t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 08:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0.3020833333333333</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2184137</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>PTS1293</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>92/6988</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salmiya </t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Front Side Stearing Wobbling &amp; All Balloon Check  </t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 08:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2164040</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>PTS1514</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>92/9495</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hasawi </t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Over Heat &amp; Left Side Break Alarm &amp; Air Leak  </t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 09:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2234048</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>PTS1457</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>92/9480</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hasawi </t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air Leak &amp; Rear Right Side Break Jam </t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.3229166666666667</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174364 </t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>PTS1214</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>92/6901</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliya </t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Break Jam &amp; Break Defect </t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 09:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0.3229166666666667</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2224020</v>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>PTS1554</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>92/9486</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliya </t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air leak , Over  heat </t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 09:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0.3277777777777778</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>2184132</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>PTS1265</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>92/6893</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Sharq</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Over heat </t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 09:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0.3506944444444444</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184540 </t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>PTS1354</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>92/9005</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Murgab to pts  </t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Air   Leaks    &amp;   Bubbling   too  Much </t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.3486111111111111</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2174046</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>PTS1579</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>92/9555</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salmiya To pts </t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Air   Leaks  &amp;  Air Compressors  Check </t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 13:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.3784722222222222</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184046 </t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>PTS1578</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>92/9554</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jleeb To pts </t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Red Yellow  Indication &amp; On  Running Time   Engine   Off  &amp;   Low  Pick up </t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.3854166666666667</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174529 </t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>MOE331</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>92/8929</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jahra To pts </t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Clutch  &amp; Low Pick up &amp; Hand  Brake </t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 9:21</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184160 </t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>PTS1426</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>92/9581</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Farwaniya </t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> water leak &amp; over heat</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="7" t="n"/>
+      <c r="K29" s="7" t="n"/>
+      <c r="L29" s="7" t="n"/>
+      <c r="M29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>TYRE, MECH</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0.3472222222222222</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>2184361</v>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>PTS1612</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Zhong tong</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Murgab to pts</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right Side Rear  wheel   Brake  Jam &amp;  Smoke  Coming </t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 10:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.3472222222222222</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234091 </t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>PTS1504</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>92/9499</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jleeb  to pts </t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Left  Side front  wheel  brake Jam &amp; Sound Coming &amp;  Rear  Both Of  side  Wheel  Brake  Defect  &amp; Check Brake Liner Replace </t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.4027777777777778</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2134474 </t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>PTS1233</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>92/6928</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maliyah to pts </t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Brake  &amp;  Hand  Brake defect &amp; rear Both Of side  4  Th  Tire   Replace  New Tire </t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 11:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.3993055555555556</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>2184152</v>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>MOE281</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>92/8878</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Salmiya  To pts</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Right  Side  Front   wheel  Brake  Jam &amp;  Front   Both Of Side Tire  Replace New </t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 12:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="7" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ELE, MECH, BODY</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 8:40</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>PTS1522</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>PTS1522</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>92/9543</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MURGAB  </t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear door defect Engine oil top up brake adjust  parking light defect  </t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-25 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
+      <c r="J36" s="7" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A18:A29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1279,17 +5849,17 @@
           <t>Work Order Status Report</t>
         </is>
       </c>
-      <c r="B1" s="24" t="n"/>
-      <c r="C1" s="24" t="n"/>
-      <c r="D1" s="24" t="n"/>
-      <c r="E1" s="24" t="n"/>
-      <c r="F1" s="24" t="n"/>
-      <c r="G1" s="24" t="n"/>
-      <c r="H1" s="24" t="n"/>
-      <c r="I1" s="24" t="n"/>
-      <c r="J1" s="24" t="n"/>
-      <c r="K1" s="24" t="n"/>
-      <c r="L1" s="25" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+      <c r="K1" s="8" t="n"/>
+      <c r="L1" s="9" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1412,7 +5982,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="n"/>
+      <c r="A4" s="10" t="n"/>
       <c r="B4" s="5" t="n">
         <v>8</v>
       </c>
@@ -1461,7 +6031,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n"/>
+      <c r="A5" s="11" t="n"/>
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
@@ -1527,7 +6097,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="n"/>
+      <c r="A7" s="10" t="n"/>
       <c r="B7" s="5" t="n">
         <v>3</v>
       </c>
@@ -1574,7 +6144,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="n"/>
+      <c r="A8" s="10" t="n"/>
       <c r="B8" s="5" t="n">
         <v>4</v>
       </c>
@@ -1623,7 +6193,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="n"/>
+      <c r="A9" s="10" t="n"/>
       <c r="B9" s="5" t="n">
         <v>6</v>
       </c>
@@ -1672,7 +6242,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="n"/>
+      <c r="A10" s="10" t="n"/>
       <c r="B10" s="5" t="n">
         <v>11</v>
       </c>
@@ -1721,7 +6291,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="n"/>
+      <c r="A11" s="10" t="n"/>
       <c r="B11" s="5" t="n">
         <v>12</v>
       </c>
@@ -1770,7 +6340,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="n"/>
+      <c r="A12" s="10" t="n"/>
       <c r="B12" s="5" t="n">
         <v>13</v>
       </c>
@@ -1819,7 +6389,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="n"/>
+      <c r="A13" s="10" t="n"/>
       <c r="B13" s="5" t="n">
         <v>14</v>
       </c>
@@ -1868,7 +6438,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="n"/>
+      <c r="A14" s="10" t="n"/>
       <c r="B14" s="5" t="n">
         <v>16</v>
       </c>
@@ -1919,7 +6489,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n"/>
+      <c r="A15" s="10" t="n"/>
       <c r="B15" s="5" t="n">
         <v>17</v>
       </c>
@@ -1970,7 +6540,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="n"/>
+      <c r="A16" s="10" t="n"/>
       <c r="B16" s="5" t="n">
         <v>18</v>
       </c>
@@ -2021,7 +6591,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="n"/>
+      <c r="A17" s="10" t="n"/>
       <c r="B17" s="5" t="n">
         <v>19</v>
       </c>
@@ -2072,7 +6642,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="n"/>
+      <c r="A18" s="10" t="n"/>
       <c r="B18" s="5" t="n">
         <v>20</v>
       </c>
@@ -2123,7 +6693,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="n"/>
+      <c r="A19" s="10" t="n"/>
       <c r="B19" s="5" t="n">
         <v>24</v>
       </c>
@@ -2174,7 +6744,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="n"/>
+      <c r="A20" s="10" t="n"/>
       <c r="B20" s="5" t="n">
         <v>25</v>
       </c>
@@ -2223,7 +6793,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="n"/>
+      <c r="A21" s="10" t="n"/>
       <c r="B21" s="5" t="n">
         <v>29</v>
       </c>
@@ -2272,7 +6842,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="n"/>
+      <c r="A22" s="10" t="n"/>
       <c r="B22" s="5" t="n">
         <v>31</v>
       </c>
@@ -2323,7 +6893,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="n"/>
+      <c r="A23" s="10" t="n"/>
       <c r="B23" s="5" t="n">
         <v>32</v>
       </c>
@@ -2374,7 +6944,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="n"/>
+      <c r="A24" s="10" t="n"/>
       <c r="B24" s="5" t="n">
         <v>34</v>
       </c>
@@ -2425,7 +6995,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="n"/>
+      <c r="A25" s="10" t="n"/>
       <c r="B25" s="5" t="n">
         <v>35</v>
       </c>
@@ -2476,7 +7046,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="n"/>
+      <c r="A26" s="10" t="n"/>
       <c r="B26" s="5" t="n">
         <v>36</v>
       </c>
@@ -2529,7 +7099,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="26" t="n"/>
+      <c r="A27" s="10" t="n"/>
       <c r="B27" s="5" t="n">
         <v>37</v>
       </c>
@@ -2582,7 +7152,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="n"/>
+      <c r="A28" s="11" t="n"/>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="n"/>
@@ -2650,7 +7220,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="n"/>
+      <c r="A30" s="10" t="n"/>
       <c r="B30" s="5" t="n">
         <v>15</v>
       </c>
@@ -2701,7 +7271,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="n"/>
+      <c r="A31" s="10" t="n"/>
       <c r="B31" s="5" t="n">
         <v>26</v>
       </c>
@@ -2754,7 +7324,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="n"/>
+      <c r="A32" s="11" t="n"/>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="n"/>
@@ -2822,7 +7392,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="n"/>
+      <c r="A34" s="10" t="n"/>
       <c r="B34" s="5" t="n">
         <v>9</v>
       </c>
@@ -2871,7 +7441,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26" t="n"/>
+      <c r="A35" s="10" t="n"/>
       <c r="B35" s="5" t="n">
         <v>10</v>
       </c>
@@ -2920,7 +7490,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="n"/>
+      <c r="A36" s="10" t="n"/>
       <c r="B36" s="5" t="n">
         <v>23</v>
       </c>
@@ -2971,7 +7541,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="n"/>
+      <c r="A37" s="11" t="n"/>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="n"/>
@@ -3039,7 +7609,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="27" t="n"/>
+      <c r="A39" s="11" t="n"/>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="n"/>
@@ -3107,7 +7677,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="27" t="n"/>
+      <c r="A41" s="11" t="n"/>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="n"/>
@@ -3177,7 +7747,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="26" t="n"/>
+      <c r="A43" s="10" t="n"/>
       <c r="B43" s="5" t="n">
         <v>33</v>
       </c>
@@ -3228,7 +7798,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="27" t="n"/>
+      <c r="A44" s="11" t="n"/>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="n"/>
@@ -3296,7 +7866,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="27" t="n"/>
+      <c r="A46" s="11" t="n"/>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="n"/>
@@ -3366,7 +7936,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="27" t="n"/>
+      <c r="A48" s="11" t="n"/>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="n"/>
@@ -3395,4 +7965,1541 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="163" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Work Order Status Report</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+      <c r="K1" s="8" t="n"/>
+      <c r="L1" s="9" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Date of B/D</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Time of B/D</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Driver Emp No #</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Asset Number</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Bus No.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Type Of B/D</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Operation Action</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Re-Operations time</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>W/S Comments</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>workshop reported time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>MECH</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2234067</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>PTS1292</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>92/6963</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PTS G1 </t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Back Right Side  Balloon Defect &amp; Air Leak &amp; Break Adjust</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 08:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234068 </t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>PTS1310</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>92/6978</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air Leak &amp; Oil Top Up </t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.2847222222222222</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2184292</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>PTS1517</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>92/9542</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PTS G1 </t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air Leak </t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2224062 </t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>PTS1573</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>92/9455</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sharg </t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air Leak </t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 08:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.3020833333333333</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2154067 </t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>PTS1399</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>92/9528</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rigai </t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Left Side Balloon Defect </t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.3090277777777778</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2224063</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>PTS1217</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>92/6878</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sharg </t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Red Indication Poor Pick Up </t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2224052 </t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>PTS1309</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>92/6873</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air Leak &amp; Front Right Side Shockabserber Broken  </t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.3159722222222222</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2184116</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>PTS1436</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>92/9469</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Murughab </t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Break Jam </t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Road Side Assistant</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 08:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.3263888888888889</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174315 </t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>PTS1252</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>92/6939</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Murughab </t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Brake   Jam  &amp;  All    Lighting   Systems  </t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 10:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0.3645833333333333</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2234122</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>PTS1250</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>92/6941</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Murughab </t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Wobbling   Too  Much  &amp; Coolant  Water </t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.3784722222222222</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184085 </t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>PTS1364</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>92/9015</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Break   Jam  &amp;   Smoke    Coming </t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.3819444444444444</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184028 </t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>PTS1296</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>92/6907</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Air   Leaks   &amp;  Brake  Defect </t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 12:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2084015 </t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>PTS1258</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>92/6945</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Salmiya</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Front   Both  Of   Side  Balloon  &amp; Brake   Sound  Coming &amp;  All  Lighting  Systems  Check &amp;  Repairs </t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 13:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.4027777777777778</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2184445</v>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>MOE375</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>92/8973</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Salmiya</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air   Leaks  &amp;  Brake  Jam &amp; Check &amp; Replace  Brake  Liner </t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 11:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>ELE, TYRE, MECH</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174566 </t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>PTS1581</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>92/9576</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PTS G1 </t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Rear Right Side Outer Tire Puncher   &amp; Left Side Balloon Defect  &amp; Back Side Fan Belt Broken</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184138 </t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>MOE280</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>92/8877</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jleeb </t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A/C Defect &amp; Head Light Not Working </t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 08:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="7" t="n"/>
+      <c r="K21" s="7" t="n"/>
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>TYRE</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0.3263888888888889</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2164052</v>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>MOE359</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>92/8957</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Salmiya</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Rear Left Side Outer Tire Puncher</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 11:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0.3194444444444444</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2134405</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>PTS1365</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>92/9016</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Salmiya</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Front   Wheel   Wobbling   &amp;  Over  Heat </t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 10:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0.3368055555555556</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2115465</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>MOE360</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>92/8958</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Shuwaikh</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right  Side   Rear   Outer   Tire Blast  </t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 09:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174115 </t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>PTS1403</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>92/9442</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fahaheel  to pts </t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Left  Side Rear  Outer  Tire &amp; Right  Side Rear Inner  Tire  Puncher  &amp; Check &amp; Replace  &amp; Over   Heat  Coolant  &amp; All   Lighting   Systems   Check &amp;   Repairs </t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 10:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.3541666666666667</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2234118 </t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>PTS1459</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>92/9497</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Right   Side  Rear   Outer  Tire  Blast  Replace </t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 10:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="7" t="n"/>
+      <c r="K27" s="7" t="n"/>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>TYRE, MECH</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0.3229166666666667</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174364 </t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>PTS1214</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>92/6901</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Brake   Defect   Front   Wheel   Brake  Jam </t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Send Doha W/S</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 14:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0.3472222222222222</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184113 </t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>PTS1284</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>92/6964</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Right   Side  Rear   wheel Hub  Seal Oil Leaks  </t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0.3645833333333333</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2174177 </t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>PTS1363</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>92/9014</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Over  Heat  &amp;  Rear  wheel  Both Of Side  Brake   Defect &amp;  wiper   Check &amp; Replace </t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 10:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2224071 </t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>PTS1393</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>92/9421</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Salmiya</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Steering   wheel  Hard  Tide &amp; wobbling </t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 11:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2234070</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>PTS1253</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>92/6942</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Maliya</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Steering   wobbling   Too  Much &amp;  Brake  Defect  Rear  Both of wheel  &amp; Sound Coming  </t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Send PTS G1 W/S</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23 10:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+      <c r="J33" s="7" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A3:A17"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A18:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>